--- a/annotations Henri.xlsx
+++ b/annotations Henri.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/henrifabre/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{0B9CED24-D3D8-264F-99EE-DDD62E518CE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{4FCFAE87-371E-4944-A48E-7BCEC42C9279}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="19460" windowHeight="18000" xr2:uid="{CDECE527-FC7C-8E48-92CE-5A0AFA5F46F7}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="733" uniqueCount="255">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="900" uniqueCount="318">
   <si>
     <t>Parti</t>
   </si>
@@ -992,6 +992,206 @@
   <si>
     <t>Nous sommes un mouvement de citoyens qui, en France, en Europe et dans le monde, se forme pour défendre la trame de la République. A
 Au premier tour des élections, il faut donner un avertissement aux partis officiels.</t>
+  </si>
+  <si>
+    <t>Les hommes qui veulent servir sont, dit-on, infiniment moins nombreux que ceux qui veulent SE servir. La vie politique, hélas, offre surtout des tentations à la seconde catégorie.</t>
+  </si>
+  <si>
+    <t>Je crois que ceux qui font profession de nous gouverner le font vraiment trop mal et que leur arrogance n'a d'égale que leur ignorance. Quand j'étais petit garçon, on m'a dit que n'importe qui pouvait devenir Président et je commence à le croire!</t>
+  </si>
+  <si>
+    <t>On a réussi à convaincre nos compatriotes que la plaie hideuse du CHÔMAGE était une fatalité partagée par tous les pays industriels.</t>
+  </si>
+  <si>
+    <t>Une tragique mais totale absurdité, pour les raisons suivantes :
+1. Une armée de trois millions de chômeurs est une FORCE composée de travailleurs disponibles. Utilisés contre nos concurents dans la lutte économique, ils augmenteront la production et renforceront la compétitivité de notre économie.</t>
+  </si>
+  <si>
+    <t>Une armée de chômeurs est un facteur de FAIBLESSE. Maintenir ces malheureux dans une oisiveté coûteuse alourdit nos charges et réduit notre compétitivité.</t>
+  </si>
+  <si>
+    <t>Transformer des chômeurs en travailleurs productifs ne peut être que source de PROFIT et facteur de PUISSANCE ECONOMIQUE. Mais nous nous sommes résignés à entretenir, à grands frais, des hordes d'oisifs désespérés et souvent subversifs, l'orsqu'ils sont concentrés dans des "banlieues dépotoirs".</t>
+  </si>
+  <si>
+    <t>Que nos dirigeants s'obstinent à les payer pour qu'ils ne travaillent pas constitue le comble de la stupidité ou celui du cynisme. Ces "responsables" entraînent notre pays dans un suicide coûteux. En d'autres temps, on aurait parlé de "sabotage".</t>
+  </si>
+  <si>
+    <t>Ne pas utiliser la totalité de ses forces productives dans la guerre économique qui fait rage revient à ne pas sortir son aviation l'orsque l'ennemi franchit nos frontières avec ses chars.
+Si vous partagez ce point de vue, faites-le savoir avec votre bulletin de vote !</t>
+  </si>
+  <si>
+    <t>I l est des combats qui ne peuvent cesser, des engagements auxquels on ne doit renoncer sans se renier soi-même.</t>
+  </si>
+  <si>
+    <t>Mon engagement d'aujourd'hui traduit la même volonté : continuer avec d'autres armes, mais avec la même passion à me battre pour ce pays que j'aime et qui m'a tant donné. L'Union des Indépendants est la concrétisation de cette obligation. L'U.D.I. n'est pas un parti politique de plus.</t>
+  </si>
+  <si>
+    <t>L'U.D.I. n'est pas un parti politique de plus. Sa vocation est d'abord de rassembler, au-delà des clivages et des divisions, les Françaises et les Français qui se reconnaissent dans les valeurs traditionnelles, croient à certaines idées essentielles, et sont décidés à agir pour les voir triompher.</t>
+  </si>
+  <si>
+    <t>Je vous avais, il y a quelques mois, appelé à voter non à Maastricht. Aujourd'hui, je vous demande de me rejoindre pour établir une France forte, digne de son histoire, sûre de son destin, ouverte aux générations futures, partie d'une Europe respectueuse des identités nationales.</t>
+  </si>
+  <si>
+    <t>J'ai donc besoin de votre soutien dès le premier tour
+Merci d'avance.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mon programme : restaurer les vrais priorités dans notre circonscription.
+</t>
+  </si>
+  <si>
+    <t>· TOUS, vous avez droit à un logement décent. Or, tel n'est pas le cas.</t>
+  </si>
+  <si>
+    <t>TOUS, vous avez droit à un travail suffisamment rémunéré, sans devoir faire trois heures de trajet par jour. On en est loin.</t>
+  </si>
+  <si>
+    <t>TOUS, vous avez droit à un urbanisme équilibré et au respect de l'environnement, le tout dans la concertation avec vous. Il reste beaucoup de chemin à faire pour cela.</t>
+  </si>
+  <si>
+    <t>Beaucoup d'autres besoins ne sont pas satisfaits : mon devoir est de contribuer à résoudre tous ces problèmes qui sont les vôtres.</t>
+  </si>
+  <si>
+    <t>Mes choix nationaux sont ceux d'une gauche ouverte et équilibrée. Je n'en mentionnerai qu'un seul : le maintien et le développement de la paix dont la construction de l'Europe est un élément essentiel.</t>
+  </si>
+  <si>
+    <t>Sachez cependant que je ne me sens aucune vocation de "beni oui oui" et que je voterai selon ma conscience, en recueillant toujours votre avis.</t>
+  </si>
+  <si>
+    <t>En France, nous aimons les idées claires. Je vous en propose quelques-unes, en préalable à un choix important.</t>
+  </si>
+  <si>
+    <t>Un député, c'est avant tout un trait d'union. Une fois élus, beaucoup se font oublier jusqu'à la prochaine élection. Telle n'est pas mon intention.</t>
+  </si>
+  <si>
+    <t>Le député doit avoir vos problèmes présents à l'esprit en préparant et en votant les lois; en retour, il doit expliquer ce qui se passe en France, en Europe, dans le Monde, les évolutions de la société. Je vous écouterai, je vous informerai.</t>
+  </si>
+  <si>
+    <t>Un député, on l'a trop oublié, est d'abord là pour ses électeurs. Défendant leurs intérêts, il exprime aussi leur personnalité, leur terroir.</t>
+  </si>
+  <si>
+    <t>Nous avons nos hauts-lieux chargés d'histoire : l'Observatoire à Meudon, la Manufacture à Sèvres, le Puits-sans-Vin à Chaville, la Forêt à Marnes-la-Coquette et à Vaucresson, les Etangs de Ville d'Avray. Ils ponctueront nos actions dans les domaines de la Science, de l'Ecologie, de la Culture, de l'Initiative économique : il y a beaucoup à faire, ensemble.</t>
+  </si>
+  <si>
+    <t>Avec vous, j'agirai.</t>
+  </si>
+  <si>
+    <t>Un député, c'est aussi un recours pour résoudre vos difficultés. C'est important, en temps de crise.</t>
+  </si>
+  <si>
+    <t>Les conservateurs prennent cette circonscription pour un fief héréditaire. Qu'y ont-ils fait, eux, face aux inquiétants problèmes de société qui se profilent ? Que font-ils pour ceux, de plus en plus nombreux, que la crise tenaille ou menace ?</t>
+  </si>
+  <si>
+    <t>Que font-ils pour le logement et le travail des jeunes ? Pas grand- chose en vérité. Pour vous et pour les vôtres, j'interviendrai.</t>
+  </si>
+  <si>
+    <t>Un député, c'est enfin une personne et non une pièce anonyme au sein d'un parti.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Des erreurs, des abus ou des affaires, il y en a eu et il y en aura encore, la société humaine est ainsi faite. L'essentiel est que force reste à la Loi et que Justice se fasse. </t>
+  </si>
+  <si>
+    <t>Le citoyen doit être exigeant : on a la classe politique qu'on mérite.Pour ma part, je suis entrée dans l'Administration française parce qu'elle incarne une certaine rigueur morale. Je suis aussi républicaine et progressiste, j'en suis fière. Je saurai me montrer digne de vous.</t>
+  </si>
+  <si>
+    <t>Les Français aiment aussi le combat politique.</t>
+  </si>
+  <si>
+    <t>Il m'opposera, les 21 et 28 mars prochain, à J .- J.GUILLET. Gauche contre Droite, oui, pas n'importe quelle gauche contre n'importe quelle droite cependant.
+Je crois représenter avec Janine FORESTIER, ma suppléante, une gauche fidèle à ses idéaux, ouverte, efficace et concrète.</t>
+  </si>
+  <si>
+    <t>Une chose est sûre : si, comme je l'espère, vous me donnez la préférence, vous me trouverez, pendant cinq ans, aux rendez-vous de votre confiance.</t>
+  </si>
+  <si>
+    <t>En votant pour élire votre député le 21 mars pro- chain, vous allez décider à la fois de l'avenir de la France et de la défense de vos propres intérêts.</t>
+  </si>
+  <si>
+    <t>Je crois profondément, avec Michel Rocard, qu'il faut renouveler la politique et reconstruire une espérance civique. C'est pourquoi, à travers une campagne électorale de proximi- té, je me suis surtout attaché à écouter les attentes que vous exprimiez.</t>
+  </si>
+  <si>
+    <t>Au cours des dix dernières années, s'il est vrai que des erreurs ont été commises et des échecs rencontrés, il n'en reste pas moins que notre pays s'est modernisé et est, aujourd'hui, mieux préparé à affronter les défis de l'avenir.</t>
+  </si>
+  <si>
+    <t>Je le dis avec fierté, car avoir le courage de ses convictions, c'est le fondement de mon engagement politique.</t>
+  </si>
+  <si>
+    <t>Pour demain, la société française a plus que jamais besoin de faire marcher ensemble le progrès et la solidarité.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Développer l'égalité des chances, par la formation et le parta- ge du travail, combattre les inégalités sociales, dans le domai- ne du logement ou par une fiscalité plus juste, protéger notre environnement : il reste tant à faire pour une gauche moderne, fidèle à ses valeurs et en même temps disponible pour agir avec toutes les autres forces de progrès ! </t>
+  </si>
+  <si>
+    <t>Les progrès de la société française dépendront aussi de la construction de l'Europe, et tout particulièrement du renforcement de l'Europe sociale, pour lequel notre pays peut jouer un grand rôle.</t>
+  </si>
+  <si>
+    <t>Divisée sur son programme et entre ses responsables, l'opposition confirme que, depuis 10 ans, tout a changé en France, sauf la droite.</t>
+  </si>
+  <si>
+    <t>Je comprends donc que beaucoup s'inquiètent de ce qui pourrait advenir avec une majorité de droite arrogante et revancharde : dans notre circonscription, la seule façon utile de s'y opposer est de se rassembler, dès le 21 mars, sur ma candidature pour faire échec au député RPR sortant.</t>
+  </si>
+  <si>
+    <t>Contrat pour la France
+· protéger les citoyens
+· refuser une protection socia- le à deux vitesses, préserver notre système de retraites
+· donner de la souplesse au système éducatif, mais ampli- fier la priorité donnée à l'édu- cation nationale, creuset de l'égalité des chances</t>
+  </si>
+  <si>
+    <t>· assurer la solidarité, entre villes riches et communes moins favorisées, entre villes et campagnes</t>
+  </si>
+  <si>
+    <t>réformer la société</t>
+  </si>
+  <si>
+    <t>en développant le partage du travail pour préserver l'emploi et lutter contre le chômage</t>
+  </si>
+  <si>
+    <t>en plaçant l'environnement au cœur d'une politique de développement plus économe des richesses de la planète</t>
+  </si>
+  <si>
+    <t>en élargissant les garanties pour les citoyens, par une réfor- me de la justice et des institutions · en favorisant la construction européenne, pour la paix, le désarmement, l'action humani- taire et la solidarité avec les pays moins développés</t>
+  </si>
+  <si>
+    <t>Dans le département des Hauts-de-seine, la droite a depuis longtemps les pleins pouvoirs. Contrôlant l'immense majorité des sièges au niveau des communes, du Conseil général et du Conseil régional, des députés et sénateurs, de l'Office départemental HLM, elle a très lar- gement bénéficié des libertés nouvelles que les lois de décentralisation ont données aux élus locaux.</t>
+  </si>
+  <si>
+    <t>Au contraire, les fossés se creusent entre les villes, entre les quartiers, entre les habitants.</t>
+  </si>
+  <si>
+    <t>Logement : assurer un meilleur équilibre géographique et social par :
+- l'utilisation des terrains publics pour construire des loge- ments sociaux dans toutes les communes où il y a moins de 30% de logements sociaux et dans les pôles de dévelop- pement prioritaire (Boulogne, Nanterre, boucle nord de la Seine);</t>
+  </si>
+  <si>
+    <t>le renforcement des moyens pour les actions de dévelop- pement social des quartiers</t>
+  </si>
+  <si>
+    <t>le transfert du patrimoine de l'office départemental HLM aux communes ou à des groupements de communes</t>
+  </si>
+  <si>
+    <t>le renforcement de règles de transparence et du rôle des élus locaux pour l'attribution des logements dans le cadre de conventions signées avec l'Etat et le département.</t>
+  </si>
+  <si>
+    <t>Transports : accorder une véritable priorité aux trans- ports collectifs avec :
+- le développement de parkings à proximité des gares de métro et de RER;</t>
+  </si>
+  <si>
+    <t>la création de voies en "site propre" pour les autobus, les tramways, les cars, les vélos;</t>
+  </si>
+  <si>
+    <t>l'abandon du projet "Muse" d'autoroutes souterraines à péage et la création d'un transport en commun Nord-Sud (métro "Croix-du-Sud", liaison Issy-Plaine/ La Défense);</t>
+  </si>
+  <si>
+    <t>le bouclage de l'autoroute A 86 dans le respect de l'envi- ronnement des communes concernées.</t>
+  </si>
+  <si>
+    <t>Education : privilégier l'égalité des chances par :
+- la rénovation prioritaire des établissements scolaires dans les quartiers défavorisés;</t>
+  </si>
+  <si>
+    <t>le développement du "crédit-formation" pour donner une deuxième chance aux jeunes en situation d'échec scolaire;</t>
+  </si>
+  <si>
+    <t>l'abandon du projet de pseudo Université privée et la création de départements d'IUT à Gennevilliers et à Boulogne, dans le cadre du plan Universités 2000.</t>
   </si>
 </sst>
 </file>
@@ -1855,7 +2055,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DEC67747-52F9-1442-91C8-DD2E062F1561}">
-  <dimension ref="A1:D248"/>
+  <dimension ref="A1:D300"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="3" max="3" width="255.83203125" bestFit="1" customWidth="1"/>
@@ -5167,7 +5367,7 @@
         <v>73</v>
       </c>
       <c r="B237" t="s">
-        <v>24</v>
+        <v>66</v>
       </c>
       <c r="C237" s="1" t="s">
         <v>254</v>
@@ -5176,92 +5376,886 @@
         <v>1</v>
       </c>
     </row>
-    <row r="238" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="238" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A238" t="s">
         <v>73</v>
       </c>
       <c r="B238" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="239" spans="1:4" x14ac:dyDescent="0.2">
+        <v>66</v>
+      </c>
+      <c r="C238" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="D238">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="239" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A239" t="s">
         <v>73</v>
       </c>
       <c r="B239" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="240" spans="1:4" x14ac:dyDescent="0.2">
+        <v>66</v>
+      </c>
+      <c r="C239" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="D239">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="240" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A240" t="s">
         <v>73</v>
       </c>
       <c r="B240" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="241" spans="1:2" x14ac:dyDescent="0.2">
+        <v>66</v>
+      </c>
+      <c r="C240" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="D240">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="241" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A241" t="s">
         <v>73</v>
       </c>
       <c r="B241" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="242" spans="1:2" x14ac:dyDescent="0.2">
+        <v>66</v>
+      </c>
+      <c r="C241" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="D241">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="242" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A242" t="s">
         <v>73</v>
       </c>
       <c r="B242" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="243" spans="1:2" x14ac:dyDescent="0.2">
+        <v>66</v>
+      </c>
+      <c r="C242" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="D242">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="243" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A243" t="s">
         <v>73</v>
       </c>
       <c r="B243" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="244" spans="1:2" x14ac:dyDescent="0.2">
+        <v>66</v>
+      </c>
+      <c r="C243" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="D243">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="244" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A244" t="s">
         <v>73</v>
       </c>
       <c r="B244" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="245" spans="1:2" x14ac:dyDescent="0.2">
+        <v>66</v>
+      </c>
+      <c r="C244" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="D244">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="245" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A245" t="s">
         <v>73</v>
       </c>
       <c r="B245" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="246" spans="1:2" x14ac:dyDescent="0.2">
+        <v>66</v>
+      </c>
+      <c r="C245" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="D245">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="246" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A246" t="s">
         <v>73</v>
       </c>
       <c r="B246" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="247" spans="1:2" x14ac:dyDescent="0.2">
+        <v>66</v>
+      </c>
+      <c r="C246" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="D246">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="247" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A247" t="s">
         <v>73</v>
       </c>
       <c r="B247" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="248" spans="1:2" x14ac:dyDescent="0.2">
+        <v>66</v>
+      </c>
+      <c r="C247" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="D247">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="248" spans="1:4" ht="17" x14ac:dyDescent="0.2">
       <c r="A248" t="s">
         <v>73</v>
       </c>
       <c r="B248" t="s">
-        <v>24</v>
+        <v>66</v>
+      </c>
+      <c r="C248" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="D248">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="249" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A249" t="s">
+        <v>73</v>
+      </c>
+      <c r="B249" t="s">
+        <v>66</v>
+      </c>
+      <c r="C249" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="D249">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="250" spans="1:4" ht="34" x14ac:dyDescent="0.2">
+      <c r="A250" t="s">
+        <v>23</v>
+      </c>
+      <c r="B250" t="s">
+        <v>24</v>
+      </c>
+      <c r="C250" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="D250">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="251" spans="1:4" ht="34" x14ac:dyDescent="0.2">
+      <c r="A251" t="s">
+        <v>23</v>
+      </c>
+      <c r="B251" t="s">
+        <v>24</v>
+      </c>
+      <c r="C251" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="D251">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="252" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A252" t="s">
+        <v>23</v>
+      </c>
+      <c r="B252" t="s">
+        <v>24</v>
+      </c>
+      <c r="C252" t="s">
+        <v>269</v>
+      </c>
+      <c r="D252">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="253" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A253" t="s">
+        <v>23</v>
+      </c>
+      <c r="B253" t="s">
+        <v>24</v>
+      </c>
+      <c r="C253" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="D253">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="254" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A254" t="s">
+        <v>23</v>
+      </c>
+      <c r="B254" t="s">
+        <v>24</v>
+      </c>
+      <c r="C254" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="D254">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="255" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A255" t="s">
+        <v>23</v>
+      </c>
+      <c r="B255" t="s">
+        <v>24</v>
+      </c>
+      <c r="C255" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="D255">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="256" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A256" t="s">
+        <v>23</v>
+      </c>
+      <c r="B256" t="s">
+        <v>24</v>
+      </c>
+      <c r="C256" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="D256">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="257" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A257" t="s">
+        <v>23</v>
+      </c>
+      <c r="B257" t="s">
+        <v>24</v>
+      </c>
+      <c r="C257" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="D257">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="258" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A258" t="s">
+        <v>23</v>
+      </c>
+      <c r="B258" t="s">
+        <v>24</v>
+      </c>
+      <c r="C258" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="D258">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="259" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A259" t="s">
+        <v>23</v>
+      </c>
+      <c r="B259" t="s">
+        <v>24</v>
+      </c>
+      <c r="C259" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="D259">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="260" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A260" t="s">
+        <v>23</v>
+      </c>
+      <c r="B260" t="s">
+        <v>24</v>
+      </c>
+      <c r="C260" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="D260">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="261" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A261" t="s">
+        <v>23</v>
+      </c>
+      <c r="B261" t="s">
+        <v>24</v>
+      </c>
+      <c r="C261" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="D261">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="262" spans="1:4" ht="34" x14ac:dyDescent="0.2">
+      <c r="A262" t="s">
+        <v>23</v>
+      </c>
+      <c r="B262" t="s">
+        <v>24</v>
+      </c>
+      <c r="C262" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="D262">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="263" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A263" t="s">
+        <v>23</v>
+      </c>
+      <c r="B263" t="s">
+        <v>24</v>
+      </c>
+      <c r="C263" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="D263">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="264" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A264" t="s">
+        <v>23</v>
+      </c>
+      <c r="B264" t="s">
+        <v>24</v>
+      </c>
+      <c r="C264" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="D264">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="265" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A265" t="s">
+        <v>23</v>
+      </c>
+      <c r="B265" t="s">
+        <v>24</v>
+      </c>
+      <c r="C265" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="D265">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="266" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A266" t="s">
+        <v>23</v>
+      </c>
+      <c r="B266" t="s">
+        <v>24</v>
+      </c>
+      <c r="C266" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="D266">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="267" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A267" t="s">
+        <v>23</v>
+      </c>
+      <c r="B267" t="s">
+        <v>24</v>
+      </c>
+      <c r="C267" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="D267">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="268" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A268" t="s">
+        <v>23</v>
+      </c>
+      <c r="B268" t="s">
+        <v>24</v>
+      </c>
+      <c r="C268" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="D268">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="269" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A269" t="s">
+        <v>23</v>
+      </c>
+      <c r="B269" t="s">
+        <v>24</v>
+      </c>
+      <c r="C269" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="D269">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="270" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A270" t="s">
+        <v>23</v>
+      </c>
+      <c r="B270" t="s">
+        <v>24</v>
+      </c>
+      <c r="C270" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="D270">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="271" spans="1:4" ht="34" x14ac:dyDescent="0.2">
+      <c r="A271" t="s">
+        <v>23</v>
+      </c>
+      <c r="B271" t="s">
+        <v>24</v>
+      </c>
+      <c r="C271" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="D271">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="272" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A272" t="s">
+        <v>23</v>
+      </c>
+      <c r="B272" t="s">
+        <v>24</v>
+      </c>
+      <c r="C272" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="D272">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="273" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A273" t="s">
+        <v>239</v>
+      </c>
+      <c r="B273" t="s">
+        <v>24</v>
+      </c>
+      <c r="C273" t="s">
+        <v>290</v>
+      </c>
+      <c r="D273">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="274" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A274" t="s">
+        <v>239</v>
+      </c>
+      <c r="B274" t="s">
+        <v>24</v>
+      </c>
+      <c r="C274" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="D274">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="275" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A275" t="s">
+        <v>239</v>
+      </c>
+      <c r="B275" t="s">
+        <v>24</v>
+      </c>
+      <c r="C275" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="D275">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="276" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A276" t="s">
+        <v>239</v>
+      </c>
+      <c r="B276" t="s">
+        <v>24</v>
+      </c>
+      <c r="C276" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="D276">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="277" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A277" t="s">
+        <v>239</v>
+      </c>
+      <c r="B277" t="s">
+        <v>24</v>
+      </c>
+      <c r="C277" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="D277">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="278" spans="1:4" ht="34" x14ac:dyDescent="0.2">
+      <c r="A278" t="s">
+        <v>239</v>
+      </c>
+      <c r="B278" t="s">
+        <v>24</v>
+      </c>
+      <c r="C278" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="D278">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="279" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A279" t="s">
+        <v>239</v>
+      </c>
+      <c r="B279" t="s">
+        <v>24</v>
+      </c>
+      <c r="C279" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="D279">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="280" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A280" t="s">
+        <v>239</v>
+      </c>
+      <c r="B280" t="s">
+        <v>24</v>
+      </c>
+      <c r="C280" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="D280">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="281" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A281" t="s">
+        <v>239</v>
+      </c>
+      <c r="B281" t="s">
+        <v>24</v>
+      </c>
+      <c r="C281" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="D281">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="282" spans="1:4" ht="68" x14ac:dyDescent="0.2">
+      <c r="A282" t="s">
+        <v>239</v>
+      </c>
+      <c r="B282" t="s">
+        <v>24</v>
+      </c>
+      <c r="C282" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="D282">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="283" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A283" t="s">
+        <v>239</v>
+      </c>
+      <c r="B283" t="s">
+        <v>24</v>
+      </c>
+      <c r="C283" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="D283">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="284" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A284" t="s">
+        <v>239</v>
+      </c>
+      <c r="B284" t="s">
+        <v>24</v>
+      </c>
+      <c r="C284" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="D284">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="285" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A285" t="s">
+        <v>239</v>
+      </c>
+      <c r="B285" t="s">
+        <v>24</v>
+      </c>
+      <c r="C285" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="D285">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="286" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A286" t="s">
+        <v>239</v>
+      </c>
+      <c r="B286" t="s">
+        <v>24</v>
+      </c>
+      <c r="C286" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="D286">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="287" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A287" t="s">
+        <v>239</v>
+      </c>
+      <c r="B287" t="s">
+        <v>24</v>
+      </c>
+      <c r="C287" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="D287">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="288" spans="1:4" ht="34" x14ac:dyDescent="0.2">
+      <c r="A288" t="s">
+        <v>239</v>
+      </c>
+      <c r="B288" t="s">
+        <v>24</v>
+      </c>
+      <c r="C288" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="D288">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="289" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A289" t="s">
+        <v>239</v>
+      </c>
+      <c r="B289" t="s">
+        <v>24</v>
+      </c>
+      <c r="C289" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="D289">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="290" spans="1:4" ht="34" x14ac:dyDescent="0.2">
+      <c r="A290" t="s">
+        <v>239</v>
+      </c>
+      <c r="B290" t="s">
+        <v>24</v>
+      </c>
+      <c r="C290" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="D290">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="291" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A291" t="s">
+        <v>239</v>
+      </c>
+      <c r="B291" t="s">
+        <v>24</v>
+      </c>
+      <c r="C291" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="D291">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="292" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A292" t="s">
+        <v>239</v>
+      </c>
+      <c r="B292" t="s">
+        <v>24</v>
+      </c>
+      <c r="C292" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="D292">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="293" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A293" t="s">
+        <v>239</v>
+      </c>
+      <c r="B293" t="s">
+        <v>24</v>
+      </c>
+      <c r="C293" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="D293">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="294" spans="1:4" ht="34" x14ac:dyDescent="0.2">
+      <c r="A294" t="s">
+        <v>239</v>
+      </c>
+      <c r="B294" t="s">
+        <v>24</v>
+      </c>
+      <c r="C294" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="D294">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="295" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A295" t="s">
+        <v>239</v>
+      </c>
+      <c r="B295" t="s">
+        <v>24</v>
+      </c>
+      <c r="C295" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="D295">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="296" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A296" t="s">
+        <v>239</v>
+      </c>
+      <c r="B296" t="s">
+        <v>24</v>
+      </c>
+      <c r="C296" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="D296">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="297" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A297" t="s">
+        <v>239</v>
+      </c>
+      <c r="B297" t="s">
+        <v>24</v>
+      </c>
+      <c r="C297" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="D297">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="298" spans="1:4" ht="34" x14ac:dyDescent="0.2">
+      <c r="A298" t="s">
+        <v>239</v>
+      </c>
+      <c r="B298" t="s">
+        <v>24</v>
+      </c>
+      <c r="C298" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="D298">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="299" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A299" t="s">
+        <v>239</v>
+      </c>
+      <c r="B299" t="s">
+        <v>24</v>
+      </c>
+      <c r="C299" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="D299">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="300" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="A300" t="s">
+        <v>239</v>
+      </c>
+      <c r="B300" t="s">
+        <v>24</v>
+      </c>
+      <c r="C300" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="D300">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/annotations Henri.xlsx
+++ b/annotations Henri.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jean-\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jean-\Desktop\Cours ENSAE\3A ENSAE\NLP\Projet final\NLP_ENSAE_Project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F2355CA-643E-43EE-82A0-82F3270E706F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4559BAE7-E607-4B86-ACE0-4AE942C9F61E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{CDECE527-FC7C-8E48-92CE-5A0AFA5F46F7}"/>
+    <workbookView xWindow="1776" yWindow="1776" windowWidth="17280" windowHeight="8880" xr2:uid="{CDECE527-FC7C-8E48-92CE-5A0AFA5F46F7}"/>
   </bookViews>
   <sheets>
     <sheet name="annotations Henri" sheetId="1" r:id="rId1"/>
@@ -23,12 +23,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="900" uniqueCount="318">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="901" uniqueCount="319">
   <si>
     <t>Parti</t>
-  </si>
-  <si>
-    <t>Courant politique</t>
   </si>
   <si>
     <t>Arrêter l'accroissement de la pression fiscale.</t>
@@ -1194,6 +1191,12 @@
   </si>
   <si>
     <t>C</t>
+  </si>
+  <si>
+    <t>Texte</t>
+  </si>
+  <si>
+    <t>Courant Politique</t>
   </si>
 </sst>
 </file>
@@ -2068,21 +2071,24 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>1</v>
+        <v>318</v>
       </c>
       <c r="C1" t="s">
+        <v>317</v>
+      </c>
+      <c r="D1" t="s">
         <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
         <v>4</v>
       </c>
-      <c r="B2" t="s">
-        <v>5</v>
+      <c r="C2" t="s">
+        <v>1</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -2090,13 +2096,13 @@
     </row>
     <row r="3" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
         <v>4</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" s="1" t="s">
         <v>5</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>6</v>
       </c>
       <c r="D3">
         <v>1</v>
@@ -2104,13 +2110,13 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
         <v>4</v>
       </c>
-      <c r="B4" t="s">
-        <v>5</v>
-      </c>
       <c r="C4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D4">
         <v>1</v>
@@ -2118,13 +2124,13 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
         <v>4</v>
       </c>
-      <c r="B5" t="s">
-        <v>5</v>
-      </c>
       <c r="C5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D5">
         <v>0</v>
@@ -2132,13 +2138,13 @@
     </row>
     <row r="6" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" t="s">
         <v>4</v>
       </c>
-      <c r="B6" t="s">
-        <v>5</v>
-      </c>
       <c r="C6" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D6">
         <v>1</v>
@@ -2146,13 +2152,13 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" t="s">
         <v>4</v>
       </c>
-      <c r="B7" t="s">
-        <v>5</v>
-      </c>
       <c r="C7" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D7">
         <v>1</v>
@@ -2160,13 +2166,13 @@
     </row>
     <row r="8" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" t="s">
         <v>4</v>
       </c>
-      <c r="B8" t="s">
-        <v>5</v>
-      </c>
       <c r="C8" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D8">
         <v>0</v>
@@ -2174,13 +2180,13 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9" t="s">
         <v>4</v>
       </c>
-      <c r="B9" t="s">
-        <v>5</v>
-      </c>
       <c r="C9" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D9">
         <v>1</v>
@@ -2188,13 +2194,13 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
+        <v>3</v>
+      </c>
+      <c r="B10" t="s">
         <v>4</v>
       </c>
-      <c r="B10" t="s">
-        <v>5</v>
-      </c>
       <c r="C10" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D10">
         <v>0</v>
@@ -2202,13 +2208,13 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
+        <v>3</v>
+      </c>
+      <c r="B11" t="s">
         <v>4</v>
       </c>
-      <c r="B11" t="s">
-        <v>5</v>
-      </c>
       <c r="C11" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D11">
         <v>1</v>
@@ -2216,13 +2222,13 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
+        <v>3</v>
+      </c>
+      <c r="B12" t="s">
         <v>4</v>
       </c>
-      <c r="B12" t="s">
-        <v>5</v>
-      </c>
       <c r="C12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D12">
         <v>0</v>
@@ -2230,13 +2236,13 @@
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
+        <v>3</v>
+      </c>
+      <c r="B13" t="s">
         <v>4</v>
       </c>
-      <c r="B13" t="s">
-        <v>5</v>
-      </c>
       <c r="C13" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D13">
         <v>0</v>
@@ -2244,13 +2250,13 @@
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
+        <v>3</v>
+      </c>
+      <c r="B14" t="s">
         <v>4</v>
       </c>
-      <c r="B14" t="s">
-        <v>5</v>
-      </c>
       <c r="C14" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D14">
         <v>0</v>
@@ -2258,13 +2264,13 @@
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
+        <v>3</v>
+      </c>
+      <c r="B15" t="s">
         <v>4</v>
       </c>
-      <c r="B15" t="s">
-        <v>5</v>
-      </c>
       <c r="C15" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D15">
         <v>0</v>
@@ -2272,13 +2278,13 @@
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
+        <v>3</v>
+      </c>
+      <c r="B16" t="s">
         <v>4</v>
       </c>
-      <c r="B16" t="s">
-        <v>5</v>
-      </c>
       <c r="C16" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D16">
         <v>0</v>
@@ -2286,13 +2292,13 @@
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
+        <v>3</v>
+      </c>
+      <c r="B17" t="s">
         <v>4</v>
       </c>
-      <c r="B17" t="s">
-        <v>5</v>
-      </c>
       <c r="C17" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D17">
         <v>1</v>
@@ -2300,13 +2306,13 @@
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
+        <v>3</v>
+      </c>
+      <c r="B18" t="s">
         <v>4</v>
       </c>
-      <c r="B18" t="s">
-        <v>5</v>
-      </c>
       <c r="C18" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D18">
         <v>1</v>
@@ -2314,13 +2320,13 @@
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B19" t="s">
         <v>4</v>
       </c>
-      <c r="B19" t="s">
-        <v>5</v>
-      </c>
       <c r="C19" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D19">
         <v>1</v>
@@ -2328,13 +2334,13 @@
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
+        <v>22</v>
+      </c>
+      <c r="B20" t="s">
+        <v>314</v>
+      </c>
+      <c r="C20" t="s">
         <v>23</v>
-      </c>
-      <c r="B20" t="s">
-        <v>315</v>
-      </c>
-      <c r="C20" t="s">
-        <v>24</v>
       </c>
       <c r="D20">
         <v>1</v>
@@ -2342,13 +2348,13 @@
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B21" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C21" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D21">
         <v>1</v>
@@ -2356,13 +2362,13 @@
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B22" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C22" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D22">
         <v>1</v>
@@ -2370,13 +2376,13 @@
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C23" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D23">
         <v>1</v>
@@ -2384,13 +2390,13 @@
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C24" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D24">
         <v>1</v>
@@ -2398,13 +2404,13 @@
     </row>
     <row r="25" spans="1:4" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
+        <v>28</v>
+      </c>
+      <c r="B25" t="s">
         <v>29</v>
       </c>
-      <c r="B25" t="s">
+      <c r="C25" s="1" t="s">
         <v>30</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>31</v>
       </c>
       <c r="D25">
         <v>1</v>
@@ -2412,13 +2418,13 @@
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
+        <v>28</v>
+      </c>
+      <c r="B26" t="s">
         <v>29</v>
       </c>
-      <c r="B26" t="s">
-        <v>30</v>
-      </c>
       <c r="C26" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D26">
         <v>1</v>
@@ -2426,13 +2432,13 @@
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
+        <v>28</v>
+      </c>
+      <c r="B27" t="s">
         <v>29</v>
       </c>
-      <c r="B27" t="s">
-        <v>30</v>
-      </c>
       <c r="C27" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D27">
         <v>1</v>
@@ -2440,13 +2446,13 @@
     </row>
     <row r="28" spans="1:4" ht="78" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
+        <v>28</v>
+      </c>
+      <c r="B28" t="s">
         <v>29</v>
       </c>
-      <c r="B28" t="s">
-        <v>30</v>
-      </c>
       <c r="C28" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D28">
         <v>0</v>
@@ -2454,13 +2460,13 @@
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
+        <v>28</v>
+      </c>
+      <c r="B29" t="s">
         <v>29</v>
       </c>
-      <c r="B29" t="s">
-        <v>30</v>
-      </c>
       <c r="C29" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D29">
         <v>1</v>
@@ -2468,13 +2474,13 @@
     </row>
     <row r="30" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
+        <v>28</v>
+      </c>
+      <c r="B30" t="s">
         <v>29</v>
       </c>
-      <c r="B30" t="s">
-        <v>30</v>
-      </c>
       <c r="C30" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D30">
         <v>0</v>
@@ -2482,13 +2488,13 @@
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
+        <v>28</v>
+      </c>
+      <c r="B31" t="s">
         <v>29</v>
       </c>
-      <c r="B31" t="s">
-        <v>30</v>
-      </c>
       <c r="C31" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D31">
         <v>0</v>
@@ -2496,13 +2502,13 @@
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
+        <v>28</v>
+      </c>
+      <c r="B32" t="s">
         <v>29</v>
       </c>
-      <c r="B32" t="s">
-        <v>30</v>
-      </c>
       <c r="C32" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D32">
         <v>0</v>
@@ -2510,13 +2516,13 @@
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
+        <v>28</v>
+      </c>
+      <c r="B33" t="s">
         <v>29</v>
       </c>
-      <c r="B33" t="s">
-        <v>30</v>
-      </c>
       <c r="C33" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D33">
         <v>0</v>
@@ -2524,13 +2530,13 @@
     </row>
     <row r="34" spans="1:4" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
+        <v>28</v>
+      </c>
+      <c r="B34" t="s">
         <v>29</v>
       </c>
-      <c r="B34" t="s">
-        <v>30</v>
-      </c>
       <c r="C34" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D34">
         <v>0</v>
@@ -2538,13 +2544,13 @@
     </row>
     <row r="35" spans="1:4" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
+        <v>28</v>
+      </c>
+      <c r="B35" t="s">
         <v>29</v>
       </c>
-      <c r="B35" t="s">
-        <v>30</v>
-      </c>
       <c r="C35" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D35">
         <v>0</v>
@@ -2552,13 +2558,13 @@
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
+        <v>28</v>
+      </c>
+      <c r="B36" t="s">
         <v>29</v>
       </c>
-      <c r="B36" t="s">
-        <v>30</v>
-      </c>
       <c r="C36" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D36">
         <v>1</v>
@@ -2566,13 +2572,13 @@
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
+        <v>28</v>
+      </c>
+      <c r="B37" t="s">
         <v>29</v>
       </c>
-      <c r="B37" t="s">
-        <v>30</v>
-      </c>
       <c r="C37" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D37">
         <v>0</v>
@@ -2580,13 +2586,13 @@
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
+        <v>28</v>
+      </c>
+      <c r="B38" t="s">
         <v>29</v>
       </c>
-      <c r="B38" t="s">
-        <v>30</v>
-      </c>
       <c r="C38" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D38">
         <v>0</v>
@@ -2594,13 +2600,13 @@
     </row>
     <row r="39" spans="1:4" ht="93.6" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
+        <v>28</v>
+      </c>
+      <c r="B39" t="s">
         <v>29</v>
       </c>
-      <c r="B39" t="s">
-        <v>30</v>
-      </c>
       <c r="C39" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D39">
         <v>1</v>
@@ -2608,13 +2614,13 @@
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
+        <v>45</v>
+      </c>
+      <c r="B40" t="s">
+        <v>314</v>
+      </c>
+      <c r="C40" t="s">
         <v>46</v>
-      </c>
-      <c r="B40" t="s">
-        <v>315</v>
-      </c>
-      <c r="C40" t="s">
-        <v>47</v>
       </c>
       <c r="D40">
         <v>1</v>
@@ -2622,13 +2628,13 @@
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B41" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C41" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D41">
         <v>1</v>
@@ -2636,13 +2642,13 @@
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B42" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C42" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D42">
         <v>1</v>
@@ -2650,13 +2656,13 @@
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B43" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C43" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D43">
         <v>1</v>
@@ -2664,13 +2670,13 @@
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B44" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C44" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D44">
         <v>1</v>
@@ -2678,13 +2684,13 @@
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B45" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C45" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D45">
         <v>1</v>
@@ -2692,13 +2698,13 @@
     </row>
     <row r="46" spans="1:4" ht="93.6" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B46" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D46">
         <v>1</v>
@@ -2706,13 +2712,13 @@
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B47" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C47" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D47">
         <v>1</v>
@@ -2720,13 +2726,13 @@
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B48" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C48" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D48">
         <v>0</v>
@@ -2734,13 +2740,13 @@
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B49" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C49" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D49">
         <v>0</v>
@@ -2748,13 +2754,13 @@
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B50" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C50" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D50">
         <v>0</v>
@@ -2762,13 +2768,13 @@
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B51" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C51" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D51">
         <v>0</v>
@@ -2776,13 +2782,13 @@
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B52" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C52" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D52">
         <v>0</v>
@@ -2790,13 +2796,13 @@
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B53" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C53" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D53">
         <v>0</v>
@@ -2804,13 +2810,13 @@
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B54" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C54" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D54">
         <v>0</v>
@@ -2818,13 +2824,13 @@
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B55" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C55" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D55">
         <v>0</v>
@@ -2832,13 +2838,13 @@
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B56" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C56" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D56">
         <v>0</v>
@@ -2846,13 +2852,13 @@
     </row>
     <row r="57" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B57" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D57">
         <v>1</v>
@@ -2860,13 +2866,13 @@
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
+        <v>63</v>
+      </c>
+      <c r="B58" t="s">
+        <v>315</v>
+      </c>
+      <c r="C58" t="s">
         <v>64</v>
-      </c>
-      <c r="B58" t="s">
-        <v>316</v>
-      </c>
-      <c r="C58" t="s">
-        <v>65</v>
       </c>
       <c r="D58">
         <v>1</v>
@@ -2874,13 +2880,13 @@
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B59" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C59" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D59">
         <v>1</v>
@@ -2888,13 +2894,13 @@
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B60" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C60" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D60">
         <v>1</v>
@@ -2902,13 +2908,13 @@
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B61" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C61" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D61">
         <v>1</v>
@@ -2916,13 +2922,13 @@
     </row>
     <row r="62" spans="1:4" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B62" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D62">
         <v>1</v>
@@ -2930,13 +2936,13 @@
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B63" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C63" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D63">
         <v>1</v>
@@ -2944,13 +2950,13 @@
     </row>
     <row r="64" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
+        <v>70</v>
+      </c>
+      <c r="B64" t="s">
+        <v>314</v>
+      </c>
+      <c r="C64" s="1" t="s">
         <v>71</v>
-      </c>
-      <c r="B64" t="s">
-        <v>315</v>
-      </c>
-      <c r="C64" s="1" t="s">
-        <v>72</v>
       </c>
       <c r="D64">
         <v>0</v>
@@ -2958,13 +2964,13 @@
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B65" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C65" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D65">
         <v>1</v>
@@ -2972,13 +2978,13 @@
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B66" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C66" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D66">
         <v>1</v>
@@ -2986,13 +2992,13 @@
     </row>
     <row r="67" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B67" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D67">
         <v>0</v>
@@ -3000,13 +3006,13 @@
     </row>
     <row r="68" spans="1:4" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B68" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D68">
         <v>0</v>
@@ -3014,13 +3020,13 @@
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B69" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C69" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D69">
         <v>0</v>
@@ -3028,13 +3034,13 @@
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B70" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C70" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D70">
         <v>0</v>
@@ -3042,13 +3048,13 @@
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B71" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C71" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D71">
         <v>1</v>
@@ -3056,13 +3062,13 @@
     </row>
     <row r="72" spans="1:4" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B72" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D72">
         <v>0</v>
@@ -3070,13 +3076,13 @@
     </row>
     <row r="73" spans="1:4" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B73" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D73">
         <v>1</v>
@@ -3084,13 +3090,13 @@
     </row>
     <row r="74" spans="1:4" ht="78" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B74" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D74">
         <v>1</v>
@@ -3098,13 +3104,13 @@
     </row>
     <row r="75" spans="1:4" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B75" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D75">
         <v>1</v>
@@ -3112,13 +3118,13 @@
     </row>
     <row r="76" spans="1:4" ht="93.6" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B76" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D76">
         <v>1</v>
@@ -3126,13 +3132,13 @@
     </row>
     <row r="77" spans="1:4" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B77" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D77">
         <v>1</v>
@@ -3140,13 +3146,13 @@
     </row>
     <row r="78" spans="1:4" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B78" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D78">
         <v>1</v>
@@ -3154,13 +3160,13 @@
     </row>
     <row r="79" spans="1:4" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B79" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D79">
         <v>1</v>
@@ -3168,13 +3174,13 @@
     </row>
     <row r="80" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B80" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D80">
         <v>1</v>
@@ -3182,13 +3188,13 @@
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B81" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C81" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D81">
         <v>0</v>
@@ -3196,13 +3202,13 @@
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B82" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C82" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D82">
         <v>1</v>
@@ -3210,13 +3216,13 @@
     </row>
     <row r="83" spans="1:4" ht="78" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B83" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D83">
         <v>1</v>
@@ -3224,13 +3230,13 @@
     </row>
     <row r="84" spans="1:4" ht="78" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B84" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D84">
         <v>1</v>
@@ -3238,13 +3244,13 @@
     </row>
     <row r="85" spans="1:4" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B85" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D85">
         <v>1</v>
@@ -3252,13 +3258,13 @@
     </row>
     <row r="86" spans="1:4" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B86" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D86">
         <v>1</v>
@@ -3266,13 +3272,13 @@
     </row>
     <row r="87" spans="1:4" ht="78" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B87" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D87">
         <v>1</v>
@@ -3280,13 +3286,13 @@
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B88" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C88" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D88">
         <v>1</v>
@@ -3294,13 +3300,13 @@
     </row>
     <row r="89" spans="1:4" ht="140.4" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B89" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D89">
         <v>1</v>
@@ -3308,13 +3314,13 @@
     </row>
     <row r="90" spans="1:4" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B90" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D90">
         <v>1</v>
@@ -3322,13 +3328,13 @@
     </row>
     <row r="91" spans="1:4" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B91" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D91">
         <v>1</v>
@@ -3336,13 +3342,13 @@
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
+        <v>99</v>
+      </c>
+      <c r="B92" t="s">
+        <v>315</v>
+      </c>
+      <c r="C92" t="s">
         <v>100</v>
-      </c>
-      <c r="B92" t="s">
-        <v>316</v>
-      </c>
-      <c r="C92" t="s">
-        <v>101</v>
       </c>
       <c r="D92">
         <v>1</v>
@@ -3350,13 +3356,13 @@
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B93" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C93" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D93">
         <v>1</v>
@@ -3364,13 +3370,13 @@
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B94" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C94" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D94">
         <v>1</v>
@@ -3378,13 +3384,13 @@
     </row>
     <row r="95" spans="1:4" ht="124.8" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B95" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D95">
         <v>1</v>
@@ -3392,13 +3398,13 @@
     </row>
     <row r="96" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B96" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D96">
         <v>1</v>
@@ -3406,13 +3412,13 @@
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B97" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C97" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D97">
         <v>1</v>
@@ -3420,13 +3426,13 @@
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B98" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C98" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D98">
         <v>1</v>
@@ -3434,13 +3440,13 @@
     </row>
     <row r="99" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B99" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D99">
         <v>1</v>
@@ -3448,13 +3454,13 @@
     </row>
     <row r="100" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
+        <v>108</v>
+      </c>
+      <c r="B100" t="s">
+        <v>4</v>
+      </c>
+      <c r="C100" s="1" t="s">
         <v>109</v>
-      </c>
-      <c r="B100" t="s">
-        <v>5</v>
-      </c>
-      <c r="C100" s="1" t="s">
-        <v>110</v>
       </c>
       <c r="D100">
         <v>1</v>
@@ -3462,13 +3468,13 @@
     </row>
     <row r="101" spans="1:4" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B101" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D101">
         <v>0</v>
@@ -3476,13 +3482,13 @@
     </row>
     <row r="102" spans="1:4" ht="187.2" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B102" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D102">
         <v>0</v>
@@ -3490,13 +3496,13 @@
     </row>
     <row r="103" spans="1:4" ht="78" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B103" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D103">
         <v>1</v>
@@ -3504,13 +3510,13 @@
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B104" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C104" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D104">
         <v>1</v>
@@ -3518,13 +3524,13 @@
     </row>
     <row r="105" spans="1:4" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B105" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D105">
         <v>1</v>
@@ -3532,13 +3538,13 @@
     </row>
     <row r="106" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B106" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D106">
         <v>1</v>
@@ -3546,13 +3552,13 @@
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B107" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C107" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D107">
         <v>1</v>
@@ -3560,13 +3566,13 @@
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B108" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C108" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D108">
         <v>0</v>
@@ -3574,13 +3580,13 @@
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B109" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C109" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D109">
         <v>1</v>
@@ -3588,13 +3594,13 @@
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B110" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C110" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D110">
         <v>0</v>
@@ -3602,13 +3608,13 @@
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B111" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C111" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D111">
         <v>1</v>
@@ -3616,13 +3622,13 @@
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B112" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C112" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D112">
         <v>1</v>
@@ -3630,13 +3636,13 @@
     </row>
     <row r="113" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
+        <v>122</v>
+      </c>
+      <c r="B113" t="s">
+        <v>315</v>
+      </c>
+      <c r="C113" t="s">
         <v>123</v>
-      </c>
-      <c r="B113" t="s">
-        <v>316</v>
-      </c>
-      <c r="C113" t="s">
-        <v>124</v>
       </c>
       <c r="D113">
         <v>1</v>
@@ -3644,13 +3650,13 @@
     </row>
     <row r="114" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B114" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C114" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D114">
         <v>1</v>
@@ -3658,13 +3664,13 @@
     </row>
     <row r="115" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B115" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C115" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D115">
         <v>1</v>
@@ -3672,13 +3678,13 @@
     </row>
     <row r="116" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B116" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C116" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D116">
         <v>1</v>
@@ -3686,13 +3692,13 @@
     </row>
     <row r="117" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B117" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C117" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D117">
         <v>1</v>
@@ -3700,13 +3706,13 @@
     </row>
     <row r="118" spans="1:4" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B118" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C118" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D118">
         <v>0</v>
@@ -3714,13 +3720,13 @@
     </row>
     <row r="119" spans="1:4" ht="202.8" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B119" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C119" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D119">
         <v>0</v>
@@ -3728,13 +3734,13 @@
     </row>
     <row r="120" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B120" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C120" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D120">
         <v>1</v>
@@ -3742,13 +3748,13 @@
     </row>
     <row r="121" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B121" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C121" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D121">
         <v>1</v>
@@ -3756,13 +3762,13 @@
     </row>
     <row r="122" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B122" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C122" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D122">
         <v>1</v>
@@ -3770,13 +3776,13 @@
     </row>
     <row r="123" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B123" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C123" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D123">
         <v>1</v>
@@ -3784,13 +3790,13 @@
     </row>
     <row r="124" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B124" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C124" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D124">
         <v>1</v>
@@ -3798,13 +3804,13 @@
     </row>
     <row r="125" spans="1:4" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B125" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C125" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D125">
         <v>1</v>
@@ -3812,13 +3818,13 @@
     </row>
     <row r="126" spans="1:4" ht="78" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B126" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C126" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D126">
         <v>1</v>
@@ -3826,13 +3832,13 @@
     </row>
     <row r="127" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
+        <v>28</v>
+      </c>
+      <c r="B127" t="s">
         <v>29</v>
       </c>
-      <c r="B127" t="s">
-        <v>30</v>
-      </c>
       <c r="C127" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D127">
         <v>1</v>
@@ -3840,13 +3846,13 @@
     </row>
     <row r="128" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
+        <v>28</v>
+      </c>
+      <c r="B128" t="s">
         <v>29</v>
       </c>
-      <c r="B128" t="s">
-        <v>30</v>
-      </c>
       <c r="C128" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D128">
         <v>1</v>
@@ -3854,13 +3860,13 @@
     </row>
     <row r="129" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
+        <v>28</v>
+      </c>
+      <c r="B129" t="s">
         <v>29</v>
       </c>
-      <c r="B129" t="s">
-        <v>30</v>
-      </c>
       <c r="C129" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D129">
         <v>1</v>
@@ -3868,13 +3874,13 @@
     </row>
     <row r="130" spans="1:4" ht="93.6" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
+        <v>28</v>
+      </c>
+      <c r="B130" t="s">
         <v>29</v>
       </c>
-      <c r="B130" t="s">
-        <v>30</v>
-      </c>
       <c r="C130" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D130">
         <v>1</v>
@@ -3882,13 +3888,13 @@
     </row>
     <row r="131" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
+        <v>28</v>
+      </c>
+      <c r="B131" t="s">
         <v>29</v>
       </c>
-      <c r="B131" t="s">
-        <v>30</v>
-      </c>
       <c r="C131" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D131">
         <v>1</v>
@@ -3896,13 +3902,13 @@
     </row>
     <row r="132" spans="1:4" ht="109.2" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
+        <v>28</v>
+      </c>
+      <c r="B132" t="s">
         <v>29</v>
       </c>
-      <c r="B132" t="s">
-        <v>30</v>
-      </c>
       <c r="C132" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D132">
         <v>0</v>
@@ -3910,13 +3916,13 @@
     </row>
     <row r="133" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
+        <v>28</v>
+      </c>
+      <c r="B133" t="s">
         <v>29</v>
       </c>
-      <c r="B133" t="s">
-        <v>30</v>
-      </c>
       <c r="C133" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D133">
         <v>0</v>
@@ -3924,13 +3930,13 @@
     </row>
     <row r="134" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
+        <v>28</v>
+      </c>
+      <c r="B134" t="s">
         <v>29</v>
       </c>
-      <c r="B134" t="s">
-        <v>30</v>
-      </c>
       <c r="C134" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D134">
         <v>0</v>
@@ -3938,13 +3944,13 @@
     </row>
     <row r="135" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
+        <v>28</v>
+      </c>
+      <c r="B135" t="s">
         <v>29</v>
       </c>
-      <c r="B135" t="s">
-        <v>30</v>
-      </c>
       <c r="C135" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D135">
         <v>0</v>
@@ -3952,13 +3958,13 @@
     </row>
     <row r="136" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
+        <v>28</v>
+      </c>
+      <c r="B136" t="s">
         <v>29</v>
       </c>
-      <c r="B136" t="s">
-        <v>30</v>
-      </c>
       <c r="C136" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D136">
         <v>0</v>
@@ -3966,13 +3972,13 @@
     </row>
     <row r="137" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
+        <v>28</v>
+      </c>
+      <c r="B137" t="s">
         <v>29</v>
       </c>
-      <c r="B137" t="s">
-        <v>30</v>
-      </c>
       <c r="C137" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D137">
         <v>0</v>
@@ -3980,13 +3986,13 @@
     </row>
     <row r="138" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
+        <v>28</v>
+      </c>
+      <c r="B138" t="s">
         <v>29</v>
       </c>
-      <c r="B138" t="s">
-        <v>30</v>
-      </c>
       <c r="C138" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D138">
         <v>0</v>
@@ -3994,13 +4000,13 @@
     </row>
     <row r="139" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
+        <v>28</v>
+      </c>
+      <c r="B139" t="s">
         <v>29</v>
       </c>
-      <c r="B139" t="s">
-        <v>30</v>
-      </c>
       <c r="C139" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D139">
         <v>1</v>
@@ -4008,13 +4014,13 @@
     </row>
     <row r="140" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
+        <v>28</v>
+      </c>
+      <c r="B140" t="s">
         <v>29</v>
       </c>
-      <c r="B140" t="s">
-        <v>30</v>
-      </c>
       <c r="C140" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D140">
         <v>1</v>
@@ -4022,13 +4028,13 @@
     </row>
     <row r="141" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
+        <v>28</v>
+      </c>
+      <c r="B141" t="s">
         <v>29</v>
       </c>
-      <c r="B141" t="s">
-        <v>30</v>
-      </c>
       <c r="C141" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D141">
         <v>0</v>
@@ -4036,13 +4042,13 @@
     </row>
     <row r="142" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
+        <v>28</v>
+      </c>
+      <c r="B142" t="s">
         <v>29</v>
       </c>
-      <c r="B142" t="s">
-        <v>30</v>
-      </c>
       <c r="C142" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D142">
         <v>1</v>
@@ -4050,13 +4056,13 @@
     </row>
     <row r="143" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
+        <v>28</v>
+      </c>
+      <c r="B143" t="s">
         <v>29</v>
       </c>
-      <c r="B143" t="s">
-        <v>30</v>
-      </c>
       <c r="C143" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D143">
         <v>0</v>
@@ -4064,13 +4070,13 @@
     </row>
     <row r="144" spans="1:4" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
+        <v>28</v>
+      </c>
+      <c r="B144" t="s">
         <v>29</v>
       </c>
-      <c r="B144" t="s">
-        <v>30</v>
-      </c>
       <c r="C144" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D144">
         <v>0</v>
@@ -4078,13 +4084,13 @@
     </row>
     <row r="145" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
+        <v>28</v>
+      </c>
+      <c r="B145" t="s">
         <v>29</v>
       </c>
-      <c r="B145" t="s">
-        <v>30</v>
-      </c>
       <c r="C145" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D145">
         <v>1</v>
@@ -4092,13 +4098,13 @@
     </row>
     <row r="146" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
+        <v>28</v>
+      </c>
+      <c r="B146" t="s">
         <v>29</v>
       </c>
-      <c r="B146" t="s">
-        <v>30</v>
-      </c>
       <c r="C146" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D146">
         <v>1</v>
@@ -4106,13 +4112,13 @@
     </row>
     <row r="147" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
+        <v>28</v>
+      </c>
+      <c r="B147" t="s">
         <v>29</v>
       </c>
-      <c r="B147" t="s">
-        <v>30</v>
-      </c>
       <c r="C147" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D147">
         <v>1</v>
@@ -4120,13 +4126,13 @@
     </row>
     <row r="148" spans="1:4" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
+        <v>28</v>
+      </c>
+      <c r="B148" t="s">
         <v>29</v>
       </c>
-      <c r="B148" t="s">
-        <v>30</v>
-      </c>
       <c r="C148" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D148">
         <v>1</v>
@@ -4134,13 +4140,13 @@
     </row>
     <row r="149" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
+        <v>28</v>
+      </c>
+      <c r="B149" t="s">
         <v>29</v>
       </c>
-      <c r="B149" t="s">
-        <v>30</v>
-      </c>
       <c r="C149" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D149">
         <v>1</v>
@@ -4148,13 +4154,13 @@
     </row>
     <row r="150" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
+        <v>28</v>
+      </c>
+      <c r="B150" t="s">
         <v>29</v>
       </c>
-      <c r="B150" t="s">
-        <v>30</v>
-      </c>
       <c r="C150" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D150">
         <v>1</v>
@@ -4162,13 +4168,13 @@
     </row>
     <row r="151" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
+        <v>28</v>
+      </c>
+      <c r="B151" t="s">
         <v>29</v>
       </c>
-      <c r="B151" t="s">
-        <v>30</v>
-      </c>
       <c r="C151" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D151">
         <v>0</v>
@@ -4176,13 +4182,13 @@
     </row>
     <row r="152" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
+        <v>28</v>
+      </c>
+      <c r="B152" t="s">
         <v>29</v>
       </c>
-      <c r="B152" t="s">
-        <v>30</v>
-      </c>
       <c r="C152" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D152">
         <v>0</v>
@@ -4190,13 +4196,13 @@
     </row>
     <row r="153" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
+        <v>28</v>
+      </c>
+      <c r="B153" t="s">
         <v>29</v>
       </c>
-      <c r="B153" t="s">
-        <v>30</v>
-      </c>
       <c r="C153" s="1" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D153">
         <v>0</v>
@@ -4204,13 +4210,13 @@
     </row>
     <row r="154" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
+        <v>28</v>
+      </c>
+      <c r="B154" t="s">
         <v>29</v>
       </c>
-      <c r="B154" t="s">
-        <v>30</v>
-      </c>
       <c r="C154" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D154">
         <v>0</v>
@@ -4218,13 +4224,13 @@
     </row>
     <row r="155" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
+        <v>28</v>
+      </c>
+      <c r="B155" t="s">
         <v>29</v>
       </c>
-      <c r="B155" t="s">
-        <v>30</v>
-      </c>
       <c r="C155" s="1" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D155">
         <v>1</v>
@@ -4232,13 +4238,13 @@
     </row>
     <row r="156" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
+        <v>28</v>
+      </c>
+      <c r="B156" t="s">
         <v>29</v>
       </c>
-      <c r="B156" t="s">
-        <v>30</v>
-      </c>
       <c r="C156" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D156">
         <v>1</v>
@@ -4246,13 +4252,13 @@
     </row>
     <row r="157" spans="1:4" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
+        <v>28</v>
+      </c>
+      <c r="B157" t="s">
         <v>29</v>
       </c>
-      <c r="B157" t="s">
-        <v>30</v>
-      </c>
       <c r="C157" s="1" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D157">
         <v>1</v>
@@ -4260,13 +4266,13 @@
     </row>
     <row r="158" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
+        <v>168</v>
+      </c>
+      <c r="B158" t="s">
+        <v>315</v>
+      </c>
+      <c r="C158" t="s">
         <v>169</v>
-      </c>
-      <c r="B158" t="s">
-        <v>316</v>
-      </c>
-      <c r="C158" t="s">
-        <v>170</v>
       </c>
       <c r="D158">
         <v>1</v>
@@ -4274,13 +4280,13 @@
     </row>
     <row r="159" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
+        <v>28</v>
+      </c>
+      <c r="B159" t="s">
         <v>29</v>
       </c>
-      <c r="B159" t="s">
-        <v>30</v>
-      </c>
       <c r="C159" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D159">
         <v>1</v>
@@ -4288,13 +4294,13 @@
     </row>
     <row r="160" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
+        <v>28</v>
+      </c>
+      <c r="B160" t="s">
         <v>29</v>
       </c>
-      <c r="B160" t="s">
-        <v>30</v>
-      </c>
       <c r="C160" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D160">
         <v>1</v>
@@ -4302,13 +4308,13 @@
     </row>
     <row r="161" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
+        <v>172</v>
+      </c>
+      <c r="B161" t="s">
+        <v>4</v>
+      </c>
+      <c r="C161" t="s">
         <v>173</v>
-      </c>
-      <c r="B161" t="s">
-        <v>5</v>
-      </c>
-      <c r="C161" t="s">
-        <v>174</v>
       </c>
       <c r="D161">
         <v>1</v>
@@ -4316,13 +4322,13 @@
     </row>
     <row r="162" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B162" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C162" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D162">
         <v>1</v>
@@ -4330,13 +4336,13 @@
     </row>
     <row r="163" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B163" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C163" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D163">
         <v>1</v>
@@ -4344,13 +4350,13 @@
     </row>
     <row r="164" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B164" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C164" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D164">
         <v>1</v>
@@ -4358,13 +4364,13 @@
     </row>
     <row r="165" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B165" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C165" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D165">
         <v>1</v>
@@ -4372,13 +4378,13 @@
     </row>
     <row r="166" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B166" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C166" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D166">
         <v>1</v>
@@ -4386,13 +4392,13 @@
     </row>
     <row r="167" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B167" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C167" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D167">
         <v>1</v>
@@ -4400,13 +4406,13 @@
     </row>
     <row r="168" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B168" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C168" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D168">
         <v>1</v>
@@ -4414,13 +4420,13 @@
     </row>
     <row r="169" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B169" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C169" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D169">
         <v>1</v>
@@ -4428,13 +4434,13 @@
     </row>
     <row r="170" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B170" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C170" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D170">
         <v>1</v>
@@ -4442,13 +4448,13 @@
     </row>
     <row r="171" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B171" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C171" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D171">
         <v>1</v>
@@ -4456,13 +4462,13 @@
     </row>
     <row r="172" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B172" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C172" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D172">
         <v>1</v>
@@ -4470,13 +4476,13 @@
     </row>
     <row r="173" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B173" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C173" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D173">
         <v>1</v>
@@ -4484,13 +4490,13 @@
     </row>
     <row r="174" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B174" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C174" s="1" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="D174">
         <v>1</v>
@@ -4498,13 +4504,13 @@
     </row>
     <row r="175" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B175" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C175" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D175">
         <v>1</v>
@@ -4512,13 +4518,13 @@
     </row>
     <row r="176" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B176" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C176" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D176">
         <v>1</v>
@@ -4526,13 +4532,13 @@
     </row>
     <row r="177" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B177" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C177" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D177">
         <v>0</v>
@@ -4540,13 +4546,13 @@
     </row>
     <row r="178" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B178" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C178" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D178">
         <v>1</v>
@@ -4554,13 +4560,13 @@
     </row>
     <row r="179" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B179" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C179" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D179">
         <v>1</v>
@@ -4568,13 +4574,13 @@
     </row>
     <row r="180" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B180" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C180" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D180">
         <v>0</v>
@@ -4582,13 +4588,13 @@
     </row>
     <row r="181" spans="1:4" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B181" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C181" s="1" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="D181">
         <v>0</v>
@@ -4596,13 +4602,13 @@
     </row>
     <row r="182" spans="1:4" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B182" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C182" s="1" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D182">
         <v>0</v>
@@ -4610,13 +4616,13 @@
     </row>
     <row r="183" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B183" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C183" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D183">
         <v>1</v>
@@ -4624,13 +4630,13 @@
     </row>
     <row r="184" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B184" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C184" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D184">
         <v>0</v>
@@ -4638,13 +4644,13 @@
     </row>
     <row r="185" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B185" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C185" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D185">
         <v>1</v>
@@ -4652,13 +4658,13 @@
     </row>
     <row r="186" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B186" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C186" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D186">
         <v>1</v>
@@ -4666,13 +4672,13 @@
     </row>
     <row r="187" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B187" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C187" s="1" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="D187">
         <v>1</v>
@@ -4680,13 +4686,13 @@
     </row>
     <row r="188" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B188" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C188" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="D188">
         <v>1</v>
@@ -4694,13 +4700,13 @@
     </row>
     <row r="189" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B189" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C189" s="1" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D189">
         <v>0</v>
@@ -4708,13 +4714,13 @@
     </row>
     <row r="190" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B190" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C190" s="1" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D190">
         <v>1</v>
@@ -4722,13 +4728,13 @@
     </row>
     <row r="191" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B191" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C191" s="1" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D191">
         <v>1</v>
@@ -4736,13 +4742,13 @@
     </row>
     <row r="192" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B192" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C192" s="1" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D192">
         <v>1</v>
@@ -4750,13 +4756,13 @@
     </row>
     <row r="193" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B193" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C193" s="1" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="D193">
         <v>0</v>
@@ -4764,13 +4770,13 @@
     </row>
     <row r="194" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B194" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C194" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="D194">
         <v>0</v>
@@ -4778,13 +4784,13 @@
     </row>
     <row r="195" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B195" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C195" s="1" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D195">
         <v>1</v>
@@ -4792,13 +4798,13 @@
     </row>
     <row r="196" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B196" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C196" s="1" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="D196">
         <v>1</v>
@@ -4806,13 +4812,13 @@
     </row>
     <row r="197" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B197" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C197" s="1" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="D197">
         <v>1</v>
@@ -4820,13 +4826,13 @@
     </row>
     <row r="198" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B198" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C198" s="1" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D198">
         <v>1</v>
@@ -4834,13 +4840,13 @@
     </row>
     <row r="199" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B199" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C199" s="1" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="D199">
         <v>1</v>
@@ -4848,13 +4854,13 @@
     </row>
     <row r="200" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B200" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C200" s="1" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="D200">
         <v>1</v>
@@ -4862,13 +4868,13 @@
     </row>
     <row r="201" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B201" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C201" s="1" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="D201">
         <v>1</v>
@@ -4876,13 +4882,13 @@
     </row>
     <row r="202" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B202" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C202" s="1" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D202">
         <v>1</v>
@@ -4890,13 +4896,13 @@
     </row>
     <row r="203" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B203" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C203" s="1" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D203">
         <v>0</v>
@@ -4904,13 +4910,13 @@
     </row>
     <row r="204" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B204" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C204" s="1" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D204">
         <v>0</v>
@@ -4918,13 +4924,13 @@
     </row>
     <row r="205" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B205" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C205" s="1" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D205">
         <v>0</v>
@@ -4932,13 +4938,13 @@
     </row>
     <row r="206" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B206" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C206" s="1" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D206">
         <v>0</v>
@@ -4946,13 +4952,13 @@
     </row>
     <row r="207" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B207" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C207" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D207">
         <v>1</v>
@@ -4960,13 +4966,13 @@
     </row>
     <row r="208" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B208" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C208" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="D208">
         <v>0</v>
@@ -4974,13 +4980,13 @@
     </row>
     <row r="209" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B209" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C209" s="1" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="D209">
         <v>1</v>
@@ -4988,13 +4994,13 @@
     </row>
     <row r="210" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B210" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C210" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="D210">
         <v>0</v>
@@ -5002,13 +5008,13 @@
     </row>
     <row r="211" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B211" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C211" s="1" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D211">
         <v>1</v>
@@ -5016,13 +5022,13 @@
     </row>
     <row r="212" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B212" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C212" s="1" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D212">
         <v>1</v>
@@ -5030,13 +5036,13 @@
     </row>
     <row r="213" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B213" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C213" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D213">
         <v>1</v>
@@ -5044,13 +5050,13 @@
     </row>
     <row r="214" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B214" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C214" s="1" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D214">
         <v>1</v>
@@ -5058,13 +5064,13 @@
     </row>
     <row r="215" spans="1:4" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A215" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B215" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C215" s="1" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D215">
         <v>1</v>
@@ -5072,13 +5078,13 @@
     </row>
     <row r="216" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B216" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C216" s="1" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="D216">
         <v>1</v>
@@ -5086,13 +5092,13 @@
     </row>
     <row r="217" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A217" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B217" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C217" s="1" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D217">
         <v>1</v>
@@ -5100,13 +5106,13 @@
     </row>
     <row r="218" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A218" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B218" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C218" s="1" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D218">
         <v>1</v>
@@ -5114,13 +5120,13 @@
     </row>
     <row r="219" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A219" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B219" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C219" s="1" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D219">
         <v>1</v>
@@ -5128,13 +5134,13 @@
     </row>
     <row r="220" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A220" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B220" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C220" s="1" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D220">
         <v>1</v>
@@ -5142,13 +5148,13 @@
     </row>
     <row r="221" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B221" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C221" s="1" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="D221">
         <v>1</v>
@@ -5156,13 +5162,13 @@
     </row>
     <row r="222" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A222" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B222" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C222" s="1" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="D222">
         <v>1</v>
@@ -5170,13 +5176,13 @@
     </row>
     <row r="223" spans="1:4" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A223" t="s">
+        <v>235</v>
+      </c>
+      <c r="B223" t="s">
+        <v>314</v>
+      </c>
+      <c r="C223" s="1" t="s">
         <v>236</v>
-      </c>
-      <c r="B223" t="s">
-        <v>315</v>
-      </c>
-      <c r="C223" s="1" t="s">
-        <v>237</v>
       </c>
       <c r="D223">
         <v>1</v>
@@ -5184,13 +5190,13 @@
     </row>
     <row r="224" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A224" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B224" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C224" s="1" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="D224">
         <v>1</v>
@@ -5198,13 +5204,13 @@
     </row>
     <row r="225" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A225" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B225" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C225" s="1" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="D225">
         <v>1</v>
@@ -5212,13 +5218,13 @@
     </row>
     <row r="226" spans="1:4" ht="93.6" x14ac:dyDescent="0.3">
       <c r="A226" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B226" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C226" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="D226">
         <v>0</v>
@@ -5226,13 +5232,13 @@
     </row>
     <row r="227" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A227" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B227" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C227" s="1" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="D227">
         <v>1</v>
@@ -5240,13 +5246,13 @@
     </row>
     <row r="228" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A228" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B228" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C228" s="1" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="D228">
         <v>1</v>
@@ -5254,13 +5260,13 @@
     </row>
     <row r="229" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A229" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B229" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C229" s="1" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="D229">
         <v>1</v>
@@ -5268,13 +5274,13 @@
     </row>
     <row r="230" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A230" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B230" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C230" s="1" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="D230">
         <v>1</v>
@@ -5282,13 +5288,13 @@
     </row>
     <row r="231" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A231" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B231" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C231" s="1" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="D231">
         <v>1</v>
@@ -5296,13 +5302,13 @@
     </row>
     <row r="232" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A232" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B232" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C232" s="1" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D232">
         <v>1</v>
@@ -5310,13 +5316,13 @@
     </row>
     <row r="233" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A233" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B233" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C233" s="1" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="D233">
         <v>1</v>
@@ -5324,13 +5330,13 @@
     </row>
     <row r="234" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A234" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B234" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C234" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D234">
         <v>1</v>
@@ -5338,13 +5344,13 @@
     </row>
     <row r="235" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A235" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B235" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C235" s="1" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="D235">
         <v>1</v>
@@ -5352,13 +5358,13 @@
     </row>
     <row r="236" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A236" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B236" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C236" s="1" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="D236">
         <v>1</v>
@@ -5366,13 +5372,13 @@
     </row>
     <row r="237" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A237" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B237" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C237" s="1" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D237">
         <v>1</v>
@@ -5380,13 +5386,13 @@
     </row>
     <row r="238" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A238" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B238" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C238" s="1" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="D238">
         <v>1</v>
@@ -5394,13 +5400,13 @@
     </row>
     <row r="239" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A239" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B239" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C239" s="1" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D239">
         <v>1</v>
@@ -5408,13 +5414,13 @@
     </row>
     <row r="240" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A240" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B240" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C240" s="1" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D240">
         <v>1</v>
@@ -5422,13 +5428,13 @@
     </row>
     <row r="241" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A241" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B241" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C241" s="1" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D241">
         <v>1</v>
@@ -5436,13 +5442,13 @@
     </row>
     <row r="242" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A242" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B242" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C242" s="1" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="D242">
         <v>1</v>
@@ -5450,13 +5456,13 @@
     </row>
     <row r="243" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A243" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B243" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C243" s="1" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="D243">
         <v>1</v>
@@ -5464,13 +5470,13 @@
     </row>
     <row r="244" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A244" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B244" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C244" s="1" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="D244">
         <v>1</v>
@@ -5478,13 +5484,13 @@
     </row>
     <row r="245" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A245" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B245" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C245" s="1" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="D245">
         <v>1</v>
@@ -5492,13 +5498,13 @@
     </row>
     <row r="246" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A246" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B246" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C246" s="1" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D246">
         <v>1</v>
@@ -5506,13 +5512,13 @@
     </row>
     <row r="247" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A247" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B247" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C247" s="1" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D247">
         <v>1</v>
@@ -5520,13 +5526,13 @@
     </row>
     <row r="248" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A248" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B248" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C248" s="1" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D248">
         <v>1</v>
@@ -5534,13 +5540,13 @@
     </row>
     <row r="249" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A249" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B249" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C249" s="1" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D249">
         <v>1</v>
@@ -5548,13 +5554,13 @@
     </row>
     <row r="250" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A250" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B250" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C250" s="1" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="D250">
         <v>1</v>
@@ -5562,13 +5568,13 @@
     </row>
     <row r="251" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A251" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B251" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C251" s="1" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="D251">
         <v>1</v>
@@ -5576,13 +5582,13 @@
     </row>
     <row r="252" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A252" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B252" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C252" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D252">
         <v>1</v>
@@ -5590,13 +5596,13 @@
     </row>
     <row r="253" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A253" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B253" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C253" s="1" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D253">
         <v>1</v>
@@ -5604,13 +5610,13 @@
     </row>
     <row r="254" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A254" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B254" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C254" s="1" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D254">
         <v>1</v>
@@ -5618,13 +5624,13 @@
     </row>
     <row r="255" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A255" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B255" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C255" s="1" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D255">
         <v>1</v>
@@ -5632,13 +5638,13 @@
     </row>
     <row r="256" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A256" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B256" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C256" s="1" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D256">
         <v>1</v>
@@ -5646,13 +5652,13 @@
     </row>
     <row r="257" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A257" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B257" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C257" s="1" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D257">
         <v>1</v>
@@ -5660,13 +5666,13 @@
     </row>
     <row r="258" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A258" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B258" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C258" s="1" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="D258">
         <v>1</v>
@@ -5674,13 +5680,13 @@
     </row>
     <row r="259" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A259" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B259" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C259" s="1" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="D259">
         <v>1</v>
@@ -5688,13 +5694,13 @@
     </row>
     <row r="260" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A260" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B260" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C260" s="1" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D260">
         <v>1</v>
@@ -5702,13 +5708,13 @@
     </row>
     <row r="261" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A261" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B261" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C261" s="1" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D261">
         <v>1</v>
@@ -5716,13 +5722,13 @@
     </row>
     <row r="262" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A262" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B262" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C262" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="D262">
         <v>1</v>
@@ -5730,13 +5736,13 @@
     </row>
     <row r="263" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A263" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B263" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C263" s="1" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D263">
         <v>1</v>
@@ -5744,13 +5750,13 @@
     </row>
     <row r="264" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A264" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B264" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C264" s="1" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D264">
         <v>1</v>
@@ -5758,13 +5764,13 @@
     </row>
     <row r="265" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A265" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B265" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C265" s="1" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="D265">
         <v>1</v>
@@ -5772,13 +5778,13 @@
     </row>
     <row r="266" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A266" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B266" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C266" s="1" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="D266">
         <v>1</v>
@@ -5786,13 +5792,13 @@
     </row>
     <row r="267" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A267" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B267" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C267" s="1" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="D267">
         <v>1</v>
@@ -5800,13 +5806,13 @@
     </row>
     <row r="268" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A268" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B268" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C268" s="1" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="D268">
         <v>1</v>
@@ -5814,13 +5820,13 @@
     </row>
     <row r="269" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A269" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B269" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C269" s="1" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="D269">
         <v>1</v>
@@ -5828,13 +5834,13 @@
     </row>
     <row r="270" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A270" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B270" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C270" s="1" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="D270">
         <v>1</v>
@@ -5842,13 +5848,13 @@
     </row>
     <row r="271" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A271" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B271" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C271" s="1" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="D271">
         <v>1</v>
@@ -5856,13 +5862,13 @@
     </row>
     <row r="272" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A272" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B272" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C272" s="1" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D272">
         <v>1</v>
@@ -5870,13 +5876,13 @@
     </row>
     <row r="273" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A273" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B273" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C273" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="D273">
         <v>1</v>
@@ -5884,13 +5890,13 @@
     </row>
     <row r="274" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A274" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B274" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C274" s="1" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="D274">
         <v>1</v>
@@ -5898,13 +5904,13 @@
     </row>
     <row r="275" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A275" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B275" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C275" s="1" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="D275">
         <v>1</v>
@@ -5912,13 +5918,13 @@
     </row>
     <row r="276" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A276" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B276" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C276" s="1" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="D276">
         <v>1</v>
@@ -5926,13 +5932,13 @@
     </row>
     <row r="277" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A277" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B277" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C277" s="1" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="D277">
         <v>1</v>
@@ -5940,13 +5946,13 @@
     </row>
     <row r="278" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A278" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B278" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C278" s="1" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="D278">
         <v>1</v>
@@ -5954,13 +5960,13 @@
     </row>
     <row r="279" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A279" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B279" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C279" s="1" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D279">
         <v>1</v>
@@ -5968,13 +5974,13 @@
     </row>
     <row r="280" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A280" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B280" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C280" s="1" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="D280">
         <v>1</v>
@@ -5982,13 +5988,13 @@
     </row>
     <row r="281" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A281" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B281" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C281" s="1" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="D281">
         <v>1</v>
@@ -5996,13 +6002,13 @@
     </row>
     <row r="282" spans="1:4" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A282" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B282" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C282" s="1" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="D282">
         <v>1</v>
@@ -6010,13 +6016,13 @@
     </row>
     <row r="283" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A283" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B283" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C283" s="1" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="D283">
         <v>1</v>
@@ -6024,13 +6030,13 @@
     </row>
     <row r="284" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A284" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B284" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C284" s="1" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="D284">
         <v>1</v>
@@ -6038,13 +6044,13 @@
     </row>
     <row r="285" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A285" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B285" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C285" s="1" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="D285">
         <v>1</v>
@@ -6052,13 +6058,13 @@
     </row>
     <row r="286" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A286" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B286" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C286" s="1" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="D286">
         <v>1</v>
@@ -6066,13 +6072,13 @@
     </row>
     <row r="287" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A287" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B287" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C287" s="1" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="D287">
         <v>1</v>
@@ -6080,13 +6086,13 @@
     </row>
     <row r="288" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A288" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B288" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C288" s="1" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="D288">
         <v>1</v>
@@ -6094,13 +6100,13 @@
     </row>
     <row r="289" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A289" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B289" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C289" s="1" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="D289">
         <v>1</v>
@@ -6108,13 +6114,13 @@
     </row>
     <row r="290" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A290" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B290" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C290" s="1" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D290">
         <v>0</v>
@@ -6122,13 +6128,13 @@
     </row>
     <row r="291" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A291" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B291" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C291" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="D291">
         <v>1</v>
@@ -6136,13 +6142,13 @@
     </row>
     <row r="292" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A292" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B292" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C292" s="1" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="D292">
         <v>0</v>
@@ -6150,13 +6156,13 @@
     </row>
     <row r="293" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A293" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B293" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C293" s="1" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="D293">
         <v>0</v>
@@ -6164,13 +6170,13 @@
     </row>
     <row r="294" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A294" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B294" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C294" s="1" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="D294">
         <v>0</v>
@@ -6178,13 +6184,13 @@
     </row>
     <row r="295" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A295" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B295" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C295" s="1" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="D295">
         <v>0</v>
@@ -6192,13 +6198,13 @@
     </row>
     <row r="296" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A296" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B296" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C296" s="1" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="D296">
         <v>0</v>
@@ -6206,13 +6212,13 @@
     </row>
     <row r="297" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A297" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B297" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C297" s="1" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D297">
         <v>0</v>
@@ -6220,13 +6226,13 @@
     </row>
     <row r="298" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A298" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B298" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C298" s="1" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="D298">
         <v>0</v>
@@ -6234,13 +6240,13 @@
     </row>
     <row r="299" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A299" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B299" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C299" s="1" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="D299">
         <v>0</v>
@@ -6248,13 +6254,13 @@
     </row>
     <row r="300" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A300" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B300" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C300" s="1" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="D300">
         <v>0</v>
